--- a/docs/data/jp/xlsx/3104.xlsx
+++ b/docs/data/jp/xlsx/3104.xlsx
@@ -9431,7 +9431,7 @@
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>Salaries And Wages SGA</t>
+          <t>급여 및 임금</t>
         </is>
       </c>
       <c r="D108" s="20" t="n">
@@ -9578,7 +9578,7 @@
     <row r="111">
       <c r="A111" s="18" t="inlineStr">
         <is>
-          <t>Technical Research Expenses SGA</t>
+          <t>기술 연구비</t>
         </is>
       </c>
       <c r="D111" s="20" t="n">
@@ -10116,7 +10116,7 @@
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>Rent Income On Noncurrent Assets NOI</t>
+          <t>고정자산 임대료</t>
         </is>
       </c>
       <c r="C120" s="20" t="n">
@@ -10446,7 +10446,7 @@
     <row r="126">
       <c r="A126" s="18" t="inlineStr">
         <is>
-          <t>Rent Expenses On Noncurrent Assets NOE</t>
+          <t>고정자산 임대 비용</t>
         </is>
       </c>
       <c r="C126" s="20" t="n">
@@ -10526,7 +10526,7 @@
     <row r="128">
       <c r="A128" s="18" t="inlineStr">
         <is>
-          <t>Idle Asset Expenses NOE</t>
+          <t>유휴자산 제비용</t>
         </is>
       </c>
       <c r="I128" s="20" t="n">
@@ -10539,7 +10539,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>Commitment Fee NOE</t>
+          <t>커미트먼트 수수료</t>
         </is>
       </c>
       <c r="I129" s="20" t="n">
